--- a/TestData/LV_T1683_HLInternalTeam_EditAndUpdate.xlsx
+++ b/TestData/LV_T1683_HLInternalTeam_EditAndUpdate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vijay.kumar\source\repos\SalesForce_Project\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC7AFDF-3EF8-4AB1-8E6B-9E2077CC1DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{938037B6-C782-49DB-BF9C-021F374B0C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -144,9 +144,6 @@
     <t>Fee</t>
   </si>
   <si>
-    <t>BUS - Business Services</t>
-  </si>
-  <si>
     <t>Dealership &amp; Rental Services</t>
   </si>
   <si>
@@ -211,6 +208,9 @@
   </si>
   <si>
     <t>Debt Capital Markets</t>
+  </si>
+  <si>
+    <t>Business Services</t>
   </si>
 </sst>
 </file>
@@ -549,21 +549,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -574,16 +574,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAE9CDD2-29AB-475B-94EC-D336634923A3}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -594,16 +594,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3758DDA3-2214-4162-AB1B-AE0D4EA5A40B}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -614,12 +614,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -630,7 +630,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -649,31 +649,31 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AB2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="14.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.33203125" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -759,90 +759,90 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N2" t="s">
         <v>51</v>
       </c>
-      <c r="B2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L2" t="s">
-        <v>40</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="O2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="N2" t="s">
-        <v>52</v>
-      </c>
-      <c r="O2" s="4" t="s">
+      <c r="P2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="R2" t="s">
         <v>42</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="S2" t="s">
         <v>42</v>
       </c>
-      <c r="Q2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="T2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="S2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T2" s="4" t="s">
+      <c r="U2" t="s">
         <v>44</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>45</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>46</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>47</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>48</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>49</v>
       </c>
-      <c r="Z2" t="s">
-        <v>50</v>
-      </c>
       <c r="AA2" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB2" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1683_HLInternalTeam_EditAndUpdate.xlsx
+++ b/TestData/LV_T1683_HLInternalTeam_EditAndUpdate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{938037B6-C782-49DB-BF9C-021F374B0C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{271D3A6B-77FA-4AC9-96EE-B105E164CE4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -69,9 +69,6 @@
     <t>JobType</t>
   </si>
   <si>
-    <t>IndustryGroup</t>
-  </si>
-  <si>
     <t>Sector</t>
   </si>
   <si>
@@ -210,7 +207,10 @@
     <t>Debt Capital Markets</t>
   </si>
   <si>
-    <t>Business Services</t>
+    <t>IndustryGroup/HLSector</t>
+  </si>
+  <si>
+    <t>CSDN-0000007327</t>
   </si>
 </sst>
 </file>
@@ -549,21 +549,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -574,16 +574,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAE9CDD2-29AB-475B-94EC-D336634923A3}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -594,16 +594,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3758DDA3-2214-4162-AB1B-AE0D4EA5A40B}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -614,12 +614,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -630,7 +630,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -649,31 +649,31 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AB2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="14.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5546875" style="5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" customWidth="1"/>
+    <col min="26" max="26" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -684,165 +684,165 @@
         <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AB1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
         <v>57</v>
       </c>
       <c r="E2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" t="s">
         <v>35</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" t="s">
         <v>36</v>
       </c>
-      <c r="G2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" t="s">
         <v>37</v>
       </c>
-      <c r="I2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>38</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>39</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
+        <v>50</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="N2" t="s">
-        <v>51</v>
-      </c>
-      <c r="O2" s="4" t="s">
+      <c r="P2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R2" t="s">
         <v>41</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="S2" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="T2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="S2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T2" s="4" t="s">
+      <c r="U2" t="s">
         <v>43</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>44</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>45</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>46</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>47</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>48</v>
       </c>
-      <c r="Z2" t="s">
-        <v>49</v>
-      </c>
       <c r="AA2" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB2" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1683_HLInternalTeam_EditAndUpdate.xlsx
+++ b/TestData/LV_T1683_HLInternalTeam_EditAndUpdate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{271D3A6B-77FA-4AC9-96EE-B105E164CE4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D540040-F8CC-4EDB-82EC-84442FF71E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="57">
   <si>
     <t>StdUser</t>
   </si>
@@ -141,9 +141,6 @@
     <t>Fee</t>
   </si>
   <si>
-    <t>Dealership &amp; Rental Services</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
@@ -210,7 +207,7 @@
     <t>IndustryGroup/HLSector</t>
   </si>
   <si>
-    <t>CSDN-0000007327</t>
+    <t>CSDN-0000002536</t>
   </si>
 </sst>
 </file>
@@ -549,21 +546,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -574,16 +571,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAE9CDD2-29AB-475B-94EC-D336634923A3}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -594,16 +591,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3758DDA3-2214-4162-AB1B-AE0D4EA5A40B}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -614,12 +611,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -630,7 +627,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -649,31 +646,31 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AB2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="14.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.33203125" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -684,7 +681,7 @@
         <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>10</v>
@@ -759,90 +756,90 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N2" t="s">
         <v>49</v>
       </c>
-      <c r="B2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="O2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="N2" t="s">
-        <v>50</v>
-      </c>
-      <c r="O2" s="4" t="s">
+      <c r="P2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R2" t="s">
         <v>40</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="S2" t="s">
         <v>40</v>
       </c>
-      <c r="Q2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="T2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="S2" t="s">
-        <v>41</v>
-      </c>
-      <c r="T2" s="4" t="s">
+      <c r="U2" t="s">
         <v>42</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>43</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>44</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>45</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>46</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>47</v>
       </c>
-      <c r="Z2" t="s">
-        <v>48</v>
-      </c>
       <c r="AA2" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AB2" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1683_HLInternalTeam_EditAndUpdate.xlsx
+++ b/TestData/LV_T1683_HLInternalTeam_EditAndUpdate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B6A9DC-4491-4934-A062-6E3201151E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A22BBC-537B-4EEB-8568-AE6FC424D9B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -201,9 +201,6 @@
     <t>Opportunities</t>
   </si>
   <si>
-    <t>Debt Capital Markets</t>
-  </si>
-  <si>
     <t>IndustryGroup/HLSector</t>
   </si>
   <si>
@@ -211,6 +208,9 @@
   </si>
   <si>
     <t>Dealership &amp; Rental Services</t>
+  </si>
+  <si>
+    <t>Debt Financing</t>
   </si>
 </sst>
 </file>
@@ -259,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -268,7 +268,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -685,7 +684,7 @@
         <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>10</v>
@@ -768,13 +767,13 @@
         <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" t="s">
         <v>56</v>
-      </c>
-      <c r="E2" t="s">
-        <v>57</v>
       </c>
       <c r="F2" t="s">
         <v>34</v>
